--- a/artfynd/A 34816-2024 artfynd.xlsx
+++ b/artfynd/A 34816-2024 artfynd.xlsx
@@ -2396,10 +2396,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119640291</v>
+        <v>119640294</v>
       </c>
       <c r="B17" t="n">
-        <v>79144</v>
+        <v>91856</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2412,21 +2412,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508847</v>
+        <v>508900</v>
       </c>
       <c r="R17" t="n">
-        <v>7003454</v>
+        <v>7003399</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2485,15 +2485,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
-        </is>
-      </c>
-      <c r="AN17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov brandhögstubbe</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2515,10 +2507,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119640294</v>
+        <v>119640291</v>
       </c>
       <c r="B18" t="n">
-        <v>91856</v>
+        <v>79144</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2531,21 +2523,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2555,10 +2547,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508900</v>
+        <v>508847</v>
       </c>
       <c r="R18" t="n">
-        <v>7003399</v>
+        <v>7003454</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2604,7 +2596,15 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov brandhögstubbe</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3205,10 +3205,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119640292</v>
+        <v>119640275</v>
       </c>
       <c r="B24" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3221,34 +3221,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>508847</v>
+        <v>508414</v>
       </c>
       <c r="R24" t="n">
-        <v>7003454</v>
+        <v>7003632</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3294,12 +3294,15 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
-        </is>
+          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>1</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>grov brandhögstubbe och andra brandstubbar</t>
+          <t>1 substratenheter # gammal hård tallåga, hängande mot block</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3321,10 +3324,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119640275</v>
+        <v>119640286</v>
       </c>
       <c r="B25" t="n">
-        <v>78171</v>
+        <v>91856</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3337,34 +3340,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508414</v>
+        <v>508913</v>
       </c>
       <c r="R25" t="n">
-        <v>7003632</v>
+        <v>7003744</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3410,15 +3413,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
-        </is>
-      </c>
-      <c r="AN25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal hård tallåga, hängande mot block</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3440,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119640286</v>
+        <v>119640292</v>
       </c>
       <c r="B26" t="n">
-        <v>91856</v>
+        <v>78263</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3456,21 +3451,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3480,10 +3475,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508913</v>
+        <v>508847</v>
       </c>
       <c r="R26" t="n">
-        <v>7003744</v>
+        <v>7003454</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3529,7 +3524,12 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>grov brandhögstubbe och andra brandstubbar</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 34816-2024 artfynd.xlsx
+++ b/artfynd/A 34816-2024 artfynd.xlsx
@@ -2396,10 +2396,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119640294</v>
+        <v>119640291</v>
       </c>
       <c r="B17" t="n">
-        <v>91856</v>
+        <v>79144</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2412,21 +2412,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508900</v>
+        <v>508847</v>
       </c>
       <c r="R17" t="n">
-        <v>7003399</v>
+        <v>7003454</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2485,7 +2485,15 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov brandhögstubbe</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2507,10 +2515,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119640291</v>
+        <v>119640294</v>
       </c>
       <c r="B18" t="n">
-        <v>79144</v>
+        <v>91856</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2523,21 +2531,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2547,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508847</v>
+        <v>508900</v>
       </c>
       <c r="R18" t="n">
-        <v>7003454</v>
+        <v>7003399</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2596,15 +2604,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
-        </is>
-      </c>
-      <c r="AN18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov brandhögstubbe</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 34816-2024 artfynd.xlsx
+++ b/artfynd/A 34816-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119640295</v>
+        <v>119640282</v>
       </c>
       <c r="B2" t="n">
-        <v>78263</v>
+        <v>91856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508945</v>
+        <v>508587</v>
       </c>
       <c r="R2" t="n">
-        <v>7003353</v>
+        <v>7003606</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,15 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>140-årig stavatallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119640289</v>
+        <v>119640300</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508913</v>
+        <v>508953</v>
       </c>
       <c r="R3" t="n">
-        <v>7003620</v>
+        <v>7003530</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119640283</v>
+        <v>119640292</v>
       </c>
       <c r="B4" t="n">
-        <v>91834</v>
+        <v>78263</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,34 +913,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508663</v>
+        <v>508847</v>
       </c>
       <c r="R4" t="n">
-        <v>7003642</v>
+        <v>7003454</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +986,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>grov brandhögstubbe och andra brandstubbar</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1016,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119640271</v>
+        <v>119640296</v>
       </c>
       <c r="B5" t="n">
-        <v>90488</v>
+        <v>91856</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1029,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3242</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508504</v>
+        <v>508950</v>
       </c>
       <c r="R5" t="n">
-        <v>7003662</v>
+        <v>7003342</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,15 +1102,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>1 substratenheter # topp av fallen torraka, hängande mot block</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1135,7 +1124,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119640298</v>
+        <v>119640299</v>
       </c>
       <c r="B6" t="n">
         <v>78171</v>
@@ -1175,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508979</v>
+        <v>508959</v>
       </c>
       <c r="R6" t="n">
-        <v>7003452</v>
+        <v>7003489</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,11 +1217,11 @@
         </is>
       </c>
       <c r="AN6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2 substratenheter # bastanta gamla tallågor med kolade ytor</t>
+          <t>1 substratenheter # gammal tallåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1254,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119640290</v>
+        <v>119640284</v>
       </c>
       <c r="B7" t="n">
-        <v>91856</v>
+        <v>79607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,21 +1259,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1294,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508875</v>
+        <v>508846</v>
       </c>
       <c r="R7" t="n">
-        <v>7003587</v>
+        <v>7003739</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,7 +1332,15 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog, i kant mot lok med lövträd</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal senvuxen sälg</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1365,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119640285</v>
+        <v>119640273</v>
       </c>
       <c r="B8" t="n">
-        <v>79473</v>
+        <v>78171</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,34 +1378,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>388</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508873</v>
+        <v>508454</v>
       </c>
       <c r="R8" t="n">
-        <v>7003756</v>
+        <v>7003691</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,7 +1451,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
+          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
         </is>
       </c>
       <c r="AN8" t="n">
@@ -1462,7 +1459,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1 substratenheter # grovbarkig, ca 200-årig asp</t>
+          <t>1 substratenheter # gammal hård tallåga efter fallen torraka, hängande mot block</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1484,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119640299</v>
+        <v>119640283</v>
       </c>
       <c r="B9" t="n">
-        <v>78171</v>
+        <v>91834</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,34 +1497,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508959</v>
+        <v>508663</v>
       </c>
       <c r="R9" t="n">
-        <v>7003489</v>
+        <v>7003642</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,15 +1570,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>rikblockig 140-årig hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AN9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tallåga</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1603,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119640273</v>
+        <v>119640285</v>
       </c>
       <c r="B10" t="n">
-        <v>78171</v>
+        <v>79473</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,34 +1608,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>388</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508454</v>
+        <v>508873</v>
       </c>
       <c r="R10" t="n">
-        <v>7003691</v>
+        <v>7003756</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,7 +1681,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
         </is>
       </c>
       <c r="AN10" t="n">
@@ -1700,7 +1689,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal hård tallåga efter fallen torraka, hängande mot block</t>
+          <t>1 substratenheter # grovbarkig, ca 200-årig asp</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1722,7 +1711,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119640302</v>
+        <v>119640290</v>
       </c>
       <c r="B11" t="n">
         <v>91856</v>
@@ -1762,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508975</v>
+        <v>508875</v>
       </c>
       <c r="R11" t="n">
-        <v>7003554</v>
+        <v>7003587</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1833,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119640296</v>
+        <v>119640291</v>
       </c>
       <c r="B12" t="n">
-        <v>91856</v>
+        <v>79144</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1873,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508950</v>
+        <v>508847</v>
       </c>
       <c r="R12" t="n">
-        <v>7003342</v>
+        <v>7003454</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1923,6 +1912,14 @@
       <c r="AI12" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med fattigris</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov brandhögstubbe</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1944,10 +1941,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119640281</v>
+        <v>119640302</v>
       </c>
       <c r="B13" t="n">
-        <v>90807</v>
+        <v>91856</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,38 +1953,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>65</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508585</v>
+        <v>508975</v>
       </c>
       <c r="R13" t="n">
-        <v>7003583</v>
+        <v>7003554</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,15 +2030,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog på storblockig rismark</t>
-        </is>
-      </c>
-      <c r="AN13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov gammal tallåga, troligen fallen torraka</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2063,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119640282</v>
+        <v>119640293</v>
       </c>
       <c r="B14" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2079,34 +2068,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508587</v>
+        <v>508895</v>
       </c>
       <c r="R14" t="n">
-        <v>7003606</v>
+        <v>7003432</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2152,7 +2141,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på häll med lav</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2174,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119640293</v>
+        <v>119640278</v>
       </c>
       <c r="B15" t="n">
-        <v>91832</v>
+        <v>78171</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2190,34 +2179,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508895</v>
+        <v>508542</v>
       </c>
       <c r="R15" t="n">
-        <v>7003432</v>
+        <v>7003590</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2263,7 +2252,15 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>140-årig tallskog på häll med lav</t>
+          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal hård tallåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2285,10 +2282,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119640288</v>
+        <v>119640295</v>
       </c>
       <c r="B16" t="n">
-        <v>91856</v>
+        <v>78263</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,21 +2298,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2325,10 +2322,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508941</v>
+        <v>508945</v>
       </c>
       <c r="R16" t="n">
-        <v>7003619</v>
+        <v>7003353</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2374,7 +2371,15 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2396,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119640291</v>
+        <v>119640275</v>
       </c>
       <c r="B17" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2412,34 +2417,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508847</v>
+        <v>508414</v>
       </c>
       <c r="R17" t="n">
-        <v>7003454</v>
+        <v>7003632</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2485,7 +2490,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
+          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -2493,7 +2498,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov brandhögstubbe</t>
+          <t>1 substratenheter # gammal hård tallåga, hängande mot block</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2515,10 +2520,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119640294</v>
+        <v>119640289</v>
       </c>
       <c r="B18" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2531,21 +2536,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2555,10 +2560,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508900</v>
+        <v>508913</v>
       </c>
       <c r="R18" t="n">
-        <v>7003399</v>
+        <v>7003620</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2626,10 +2631,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119640284</v>
+        <v>119640298</v>
       </c>
       <c r="B19" t="n">
-        <v>79607</v>
+        <v>78171</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2642,21 +2647,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2666,10 +2671,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508846</v>
+        <v>508979</v>
       </c>
       <c r="R19" t="n">
-        <v>7003739</v>
+        <v>7003452</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2715,15 +2720,15 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>140-årig tallskog, i kant mot lok med lövträd</t>
+          <t>rikblockig 140-årig hällmarkstallskog</t>
         </is>
       </c>
       <c r="AN19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal senvuxen sälg</t>
+          <t>2 substratenheter # bastanta gamla tallågor med kolade ytor</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2864,10 +2869,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119640297</v>
+        <v>119640271</v>
       </c>
       <c r="B21" t="n">
-        <v>91884</v>
+        <v>90488</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2880,34 +2885,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>3242</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508975</v>
+        <v>508504</v>
       </c>
       <c r="R21" t="n">
-        <v>7003442</v>
+        <v>7003662</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2953,7 +2958,15 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>1 substratenheter # topp av fallen torraka, hängande mot block</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2975,10 +2988,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119640300</v>
+        <v>119640286</v>
       </c>
       <c r="B22" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,21 +3004,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3015,10 +3028,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>508953</v>
+        <v>508913</v>
       </c>
       <c r="R22" t="n">
-        <v>7003530</v>
+        <v>7003744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3086,10 +3099,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119640278</v>
+        <v>119640297</v>
       </c>
       <c r="B23" t="n">
-        <v>78171</v>
+        <v>91884</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3102,34 +3115,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>5449</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>508542</v>
+        <v>508975</v>
       </c>
       <c r="R23" t="n">
-        <v>7003590</v>
+        <v>7003442</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3175,15 +3188,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
-        </is>
-      </c>
-      <c r="AN23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal hård tallåga</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3205,10 +3210,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119640275</v>
+        <v>119640294</v>
       </c>
       <c r="B24" t="n">
-        <v>78171</v>
+        <v>91856</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3221,34 +3226,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>508414</v>
+        <v>508900</v>
       </c>
       <c r="R24" t="n">
-        <v>7003632</v>
+        <v>7003399</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3294,15 +3299,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
-        </is>
-      </c>
-      <c r="AN24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal hård tallåga, hängande mot block</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3324,10 +3321,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119640286</v>
+        <v>119640281</v>
       </c>
       <c r="B25" t="n">
-        <v>91856</v>
+        <v>90807</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,38 +3333,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2059</v>
+        <v>65</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508913</v>
+        <v>508585</v>
       </c>
       <c r="R25" t="n">
-        <v>7003744</v>
+        <v>7003583</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3413,7 +3410,15 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig stavatallskog på storblockig rismark</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov gammal tallåga, troligen fallen torraka</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3435,10 +3440,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119640292</v>
+        <v>119640288</v>
       </c>
       <c r="B26" t="n">
-        <v>78263</v>
+        <v>91856</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,21 +3456,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3475,10 +3480,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508847</v>
+        <v>508941</v>
       </c>
       <c r="R26" t="n">
-        <v>7003454</v>
+        <v>7003619</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3524,12 +3529,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>grov brandhögstubbe och andra brandstubbar</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 34816-2024 artfynd.xlsx
+++ b/artfynd/A 34816-2024 artfynd.xlsx
@@ -2401,7 +2401,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119640275</v>
+        <v>119640298</v>
       </c>
       <c r="B17" t="n">
         <v>78171</v>
@@ -2437,14 +2437,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508414</v>
+        <v>508979</v>
       </c>
       <c r="R17" t="n">
-        <v>7003632</v>
+        <v>7003452</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2490,15 +2490,15 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
+          <t>rikblockig 140-årig hällmarkstallskog</t>
         </is>
       </c>
       <c r="AN17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal hård tallåga, hängande mot block</t>
+          <t>2 substratenheter # bastanta gamla tallågor med kolade ytor</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119640289</v>
+        <v>119640275</v>
       </c>
       <c r="B18" t="n">
-        <v>91832</v>
+        <v>78171</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2536,34 +2536,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508913</v>
+        <v>508414</v>
       </c>
       <c r="R18" t="n">
-        <v>7003620</v>
+        <v>7003632</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2609,7 +2609,15 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal hård tallåga, hängande mot block</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2631,10 +2639,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119640298</v>
+        <v>119640289</v>
       </c>
       <c r="B19" t="n">
-        <v>78171</v>
+        <v>91832</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2647,21 +2655,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2671,10 +2679,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508979</v>
+        <v>508913</v>
       </c>
       <c r="R19" t="n">
-        <v>7003452</v>
+        <v>7003620</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2720,15 +2728,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>rikblockig 140-årig hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AN19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>2 substratenheter # bastanta gamla tallågor med kolade ytor</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 34816-2024 artfynd.xlsx
+++ b/artfynd/A 34816-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119640282</v>
+        <v>119640289</v>
       </c>
       <c r="B2" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508587</v>
+        <v>508913</v>
       </c>
       <c r="R2" t="n">
-        <v>7003606</v>
+        <v>7003620</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119640300</v>
+        <v>119640295</v>
       </c>
       <c r="B3" t="n">
-        <v>91884</v>
+        <v>78263</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508953</v>
+        <v>508945</v>
       </c>
       <c r="R3" t="n">
-        <v>7003530</v>
+        <v>7003353</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +875,15 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119640292</v>
+        <v>119640271</v>
       </c>
       <c r="B4" t="n">
-        <v>78263</v>
+        <v>90488</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,34 +921,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>3242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508847</v>
+        <v>508504</v>
       </c>
       <c r="R4" t="n">
-        <v>7003454</v>
+        <v>7003662</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,12 +994,15 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
-        </is>
+          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>grov brandhögstubbe och andra brandstubbar</t>
+          <t>1 substratenheter # topp av fallen torraka, hängande mot block</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1013,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119640296</v>
+        <v>119640281</v>
       </c>
       <c r="B5" t="n">
-        <v>91856</v>
+        <v>90807</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,38 +1036,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508950</v>
+        <v>508585</v>
       </c>
       <c r="R5" t="n">
-        <v>7003342</v>
+        <v>7003583</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,7 +1113,15 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
+          <t>140-årig stavatallskog på storblockig rismark</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov gammal tallåga, troligen fallen torraka</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1124,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119640299</v>
+        <v>119640292</v>
       </c>
       <c r="B6" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1164,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508959</v>
+        <v>508847</v>
       </c>
       <c r="R6" t="n">
-        <v>7003489</v>
+        <v>7003454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,15 +1232,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>rikblockig 140-årig hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AN6" t="n">
-        <v>1</v>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
+        </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal tallåga</t>
+          <t>grov brandhögstubbe och andra brandstubbar</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1243,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119640284</v>
+        <v>119640282</v>
       </c>
       <c r="B7" t="n">
-        <v>79607</v>
+        <v>91856</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,34 +1275,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508846</v>
+        <v>508587</v>
       </c>
       <c r="R7" t="n">
-        <v>7003739</v>
+        <v>7003606</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,15 +1348,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>140-årig tallskog, i kant mot lok med lövträd</t>
-        </is>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal senvuxen sälg</t>
+          <t>140-årig stavatallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1362,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119640273</v>
+        <v>119640302</v>
       </c>
       <c r="B8" t="n">
-        <v>78171</v>
+        <v>91856</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,34 +1386,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508454</v>
+        <v>508975</v>
       </c>
       <c r="R8" t="n">
-        <v>7003691</v>
+        <v>7003554</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,15 +1459,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
-        </is>
-      </c>
-      <c r="AN8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal hård tallåga efter fallen torraka, hängande mot block</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119640283</v>
+        <v>119640290</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,34 +1497,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508663</v>
+        <v>508875</v>
       </c>
       <c r="R9" t="n">
-        <v>7003642</v>
+        <v>7003587</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119640285</v>
+        <v>119640286</v>
       </c>
       <c r="B10" t="n">
-        <v>79473</v>
+        <v>91856</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,21 +1608,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>388</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508873</v>
+        <v>508913</v>
       </c>
       <c r="R10" t="n">
-        <v>7003756</v>
+        <v>7003744</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,15 +1681,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
-        </is>
-      </c>
-      <c r="AN10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grovbarkig, ca 200-årig asp</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1711,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119640290</v>
+        <v>119640287</v>
       </c>
       <c r="B11" t="n">
-        <v>91856</v>
+        <v>78171</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,21 +1719,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1751,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508875</v>
+        <v>508935</v>
       </c>
       <c r="R11" t="n">
-        <v>7003587</v>
+        <v>7003749</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,6 +1793,14 @@
       <c r="AI11" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal torr tallåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119640291</v>
+        <v>119640273</v>
       </c>
       <c r="B12" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,34 +1838,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508847</v>
+        <v>508454</v>
       </c>
       <c r="R12" t="n">
-        <v>7003454</v>
+        <v>7003691</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
+          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
         </is>
       </c>
       <c r="AN12" t="n">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov brandhögstubbe</t>
+          <t>1 substratenheter # gammal hård tallåga efter fallen torraka, hängande mot block</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119640302</v>
+        <v>119640294</v>
       </c>
       <c r="B13" t="n">
         <v>91856</v>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508975</v>
+        <v>508900</v>
       </c>
       <c r="R13" t="n">
-        <v>7003554</v>
+        <v>7003399</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119640293</v>
+        <v>119640297</v>
       </c>
       <c r="B14" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,21 +2068,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508895</v>
+        <v>508975</v>
       </c>
       <c r="R14" t="n">
-        <v>7003432</v>
+        <v>7003442</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>140-årig tallskog på häll med lav</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119640278</v>
+        <v>119640300</v>
       </c>
       <c r="B15" t="n">
-        <v>78171</v>
+        <v>91884</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,34 +2179,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>5449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508542</v>
+        <v>508953</v>
       </c>
       <c r="R15" t="n">
-        <v>7003590</v>
+        <v>7003530</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2252,15 +2252,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
-        </is>
-      </c>
-      <c r="AN15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal hård tallåga</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2282,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119640295</v>
+        <v>119640285</v>
       </c>
       <c r="B16" t="n">
-        <v>78263</v>
+        <v>79473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2298,21 +2290,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>388</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2322,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508945</v>
+        <v>508873</v>
       </c>
       <c r="R16" t="n">
-        <v>7003353</v>
+        <v>7003756</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2379,7 +2371,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>1 substratenheter # grovbarkig, ca 200-årig asp</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2401,7 +2393,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119640298</v>
+        <v>119640275</v>
       </c>
       <c r="B17" t="n">
         <v>78171</v>
@@ -2437,14 +2429,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508979</v>
+        <v>508414</v>
       </c>
       <c r="R17" t="n">
-        <v>7003452</v>
+        <v>7003632</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2490,15 +2482,15 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>rikblockig 140-årig hällmarkstallskog</t>
+          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
         </is>
       </c>
       <c r="AN17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>2 substratenheter # bastanta gamla tallågor med kolade ytor</t>
+          <t>1 substratenheter # gammal hård tallåga, hängande mot block</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2520,7 +2512,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119640275</v>
+        <v>119640299</v>
       </c>
       <c r="B18" t="n">
         <v>78171</v>
@@ -2556,14 +2548,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508414</v>
+        <v>508959</v>
       </c>
       <c r="R18" t="n">
-        <v>7003632</v>
+        <v>7003489</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2609,7 +2601,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
+          <t>rikblockig 140-årig hällmarkstallskog</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -2617,7 +2609,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal hård tallåga, hängande mot block</t>
+          <t>1 substratenheter # gammal tallåga</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2639,10 +2631,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119640289</v>
+        <v>119640296</v>
       </c>
       <c r="B19" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2655,21 +2647,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2679,10 +2671,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508913</v>
+        <v>508950</v>
       </c>
       <c r="R19" t="n">
-        <v>7003620</v>
+        <v>7003342</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2728,7 +2720,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2750,7 +2742,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119640287</v>
+        <v>119640298</v>
       </c>
       <c r="B20" t="n">
         <v>78171</v>
@@ -2790,10 +2782,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508935</v>
+        <v>508979</v>
       </c>
       <c r="R20" t="n">
-        <v>7003749</v>
+        <v>7003452</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2839,15 +2831,15 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>rikblockig 140-årig hällmarkstallskog</t>
         </is>
       </c>
       <c r="AN20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal torr tallåga</t>
+          <t>2 substratenheter # bastanta gamla tallågor med kolade ytor</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2869,10 +2861,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119640271</v>
+        <v>119640283</v>
       </c>
       <c r="B21" t="n">
-        <v>90488</v>
+        <v>91834</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2885,21 +2877,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3242</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2909,10 +2901,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508504</v>
+        <v>508663</v>
       </c>
       <c r="R21" t="n">
-        <v>7003662</v>
+        <v>7003642</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2958,15 +2950,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
-        </is>
-      </c>
-      <c r="AN21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>1 substratenheter # topp av fallen torraka, hängande mot block</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2988,10 +2972,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119640286</v>
+        <v>119640293</v>
       </c>
       <c r="B22" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3004,21 +2988,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3028,10 +3012,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>508913</v>
+        <v>508895</v>
       </c>
       <c r="R22" t="n">
-        <v>7003744</v>
+        <v>7003432</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3077,7 +3061,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på häll med lav</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3099,10 +3083,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119640297</v>
+        <v>119640278</v>
       </c>
       <c r="B23" t="n">
-        <v>91884</v>
+        <v>78171</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3115,34 +3099,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5449</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>508975</v>
+        <v>508542</v>
       </c>
       <c r="R23" t="n">
-        <v>7003442</v>
+        <v>7003590</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3188,7 +3172,15 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal hård tallåga</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3210,7 +3202,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119640294</v>
+        <v>119640288</v>
       </c>
       <c r="B24" t="n">
         <v>91856</v>
@@ -3250,10 +3242,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>508900</v>
+        <v>508941</v>
       </c>
       <c r="R24" t="n">
-        <v>7003399</v>
+        <v>7003619</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3321,10 +3313,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119640281</v>
+        <v>119640284</v>
       </c>
       <c r="B25" t="n">
-        <v>90807</v>
+        <v>79607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3333,38 +3325,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>65</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508585</v>
+        <v>508846</v>
       </c>
       <c r="R25" t="n">
-        <v>7003583</v>
+        <v>7003739</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3410,7 +3402,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog på storblockig rismark</t>
+          <t>140-årig tallskog, i kant mot lok med lövträd</t>
         </is>
       </c>
       <c r="AN25" t="n">
@@ -3418,7 +3410,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov gammal tallåga, troligen fallen torraka</t>
+          <t>1 substratenheter # gammal senvuxen sälg</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3440,10 +3432,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119640288</v>
+        <v>119640291</v>
       </c>
       <c r="B26" t="n">
-        <v>91856</v>
+        <v>79144</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3456,21 +3448,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3480,10 +3472,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508941</v>
+        <v>508847</v>
       </c>
       <c r="R26" t="n">
-        <v>7003619</v>
+        <v>7003454</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3529,7 +3521,15 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov brandhögstubbe</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 34816-2024 artfynd.xlsx
+++ b/artfynd/A 34816-2024 artfynd.xlsx
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119640281</v>
+        <v>119640292</v>
       </c>
       <c r="B5" t="n">
-        <v>90807</v>
+        <v>78263</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,38 +1036,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508585</v>
+        <v>508847</v>
       </c>
       <c r="R5" t="n">
-        <v>7003583</v>
+        <v>7003454</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,15 +1113,12 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog på storblockig rismark</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
+        </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov gammal tallåga, troligen fallen torraka</t>
+          <t>grov brandhögstubbe och andra brandstubbar</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1143,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119640292</v>
+        <v>119640281</v>
       </c>
       <c r="B6" t="n">
-        <v>78263</v>
+        <v>90807</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,38 +1152,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508847</v>
+        <v>508585</v>
       </c>
       <c r="R6" t="n">
-        <v>7003454</v>
+        <v>7003583</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,12 +1229,15 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
-        </is>
+          <t>140-årig stavatallskog på storblockig rismark</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>grov brandhögstubbe och andra brandstubbar</t>
+          <t>1 substratenheter # grov gammal tallåga, troligen fallen torraka</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119640294</v>
+        <v>119640297</v>
       </c>
       <c r="B13" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,21 +1957,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508900</v>
+        <v>508975</v>
       </c>
       <c r="R13" t="n">
-        <v>7003399</v>
+        <v>7003442</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2052,7 +2052,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119640297</v>
+        <v>119640300</v>
       </c>
       <c r="B14" t="n">
         <v>91884</v>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508975</v>
+        <v>508953</v>
       </c>
       <c r="R14" t="n">
-        <v>7003442</v>
+        <v>7003530</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119640300</v>
+        <v>119640294</v>
       </c>
       <c r="B15" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,21 +2179,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508953</v>
+        <v>508900</v>
       </c>
       <c r="R15" t="n">
-        <v>7003530</v>
+        <v>7003399</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 34816-2024 artfynd.xlsx
+++ b/artfynd/A 34816-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119640289</v>
+        <v>119640290</v>
       </c>
       <c r="B2" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508913</v>
+        <v>508875</v>
       </c>
       <c r="R2" t="n">
-        <v>7003620</v>
+        <v>7003587</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119640295</v>
+        <v>119640288</v>
       </c>
       <c r="B3" t="n">
-        <v>78263</v>
+        <v>91856</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508945</v>
+        <v>508941</v>
       </c>
       <c r="R3" t="n">
-        <v>7003353</v>
+        <v>7003619</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,15 +875,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -905,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119640271</v>
+        <v>119640293</v>
       </c>
       <c r="B4" t="n">
-        <v>90488</v>
+        <v>91832</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,34 +913,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3242</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508504</v>
+        <v>508895</v>
       </c>
       <c r="R4" t="n">
-        <v>7003662</v>
+        <v>7003432</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,15 +986,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>1 substratenheter # topp av fallen torraka, hängande mot block</t>
+          <t>140-årig tallskog på häll med lav</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1024,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119640292</v>
+        <v>119640271</v>
       </c>
       <c r="B5" t="n">
-        <v>78263</v>
+        <v>90488</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,34 +1024,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>3242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508847</v>
+        <v>508504</v>
       </c>
       <c r="R5" t="n">
-        <v>7003454</v>
+        <v>7003662</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,12 +1097,15 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
-        </is>
+          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>grov brandhögstubbe och andra brandstubbar</t>
+          <t>1 substratenheter # topp av fallen torraka, hängande mot block</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1140,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119640281</v>
+        <v>119640302</v>
       </c>
       <c r="B6" t="n">
-        <v>90807</v>
+        <v>91856</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,38 +1139,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508585</v>
+        <v>508975</v>
       </c>
       <c r="R6" t="n">
-        <v>7003583</v>
+        <v>7003554</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,15 +1216,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog på storblockig rismark</t>
-        </is>
-      </c>
-      <c r="AN6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov gammal tallåga, troligen fallen torraka</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1259,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119640282</v>
+        <v>119640292</v>
       </c>
       <c r="B7" t="n">
-        <v>91856</v>
+        <v>78263</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,34 +1254,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508587</v>
+        <v>508847</v>
       </c>
       <c r="R7" t="n">
-        <v>7003606</v>
+        <v>7003454</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1327,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>grov brandhögstubbe och andra brandstubbar</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1370,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119640302</v>
+        <v>119640289</v>
       </c>
       <c r="B8" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,21 +1370,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1410,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508975</v>
+        <v>508913</v>
       </c>
       <c r="R8" t="n">
-        <v>7003554</v>
+        <v>7003620</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119640290</v>
+        <v>119640278</v>
       </c>
       <c r="B9" t="n">
-        <v>91856</v>
+        <v>78171</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,34 +1481,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508875</v>
+        <v>508542</v>
       </c>
       <c r="R9" t="n">
-        <v>7003587</v>
+        <v>7003590</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,7 +1554,15 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal hård tallåga</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1592,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119640286</v>
+        <v>119640275</v>
       </c>
       <c r="B10" t="n">
-        <v>91856</v>
+        <v>78171</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,34 +1600,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508913</v>
+        <v>508414</v>
       </c>
       <c r="R10" t="n">
-        <v>7003744</v>
+        <v>7003632</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1673,15 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal hård tallåga, hängande mot block</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119640287</v>
+        <v>119640295</v>
       </c>
       <c r="B11" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,21 +1719,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508935</v>
+        <v>508945</v>
       </c>
       <c r="R11" t="n">
-        <v>7003749</v>
+        <v>7003353</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
         </is>
       </c>
       <c r="AN11" t="n">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal torr tallåga</t>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119640273</v>
+        <v>119640283</v>
       </c>
       <c r="B12" t="n">
-        <v>78171</v>
+        <v>91834</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508454</v>
+        <v>508663</v>
       </c>
       <c r="R12" t="n">
-        <v>7003691</v>
+        <v>7003642</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1911,15 +1911,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
-        </is>
-      </c>
-      <c r="AN12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal hård tallåga efter fallen torraka, hängande mot block</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1941,10 +1933,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119640297</v>
+        <v>119640286</v>
       </c>
       <c r="B13" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,21 +1949,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1981,10 +1973,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508975</v>
+        <v>508913</v>
       </c>
       <c r="R13" t="n">
-        <v>7003442</v>
+        <v>7003744</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2052,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119640300</v>
+        <v>119640284</v>
       </c>
       <c r="B14" t="n">
-        <v>91884</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,21 +2060,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2092,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508953</v>
+        <v>508846</v>
       </c>
       <c r="R14" t="n">
-        <v>7003530</v>
+        <v>7003739</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2141,7 +2133,15 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog, i kant mot lok med lövträd</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal senvuxen sälg</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119640294</v>
+        <v>119640287</v>
       </c>
       <c r="B15" t="n">
-        <v>91856</v>
+        <v>78171</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,21 +2179,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508900</v>
+        <v>508935</v>
       </c>
       <c r="R15" t="n">
-        <v>7003399</v>
+        <v>7003749</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2253,6 +2253,14 @@
       <c r="AI15" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal torr tallåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2393,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119640275</v>
+        <v>119640300</v>
       </c>
       <c r="B17" t="n">
-        <v>78171</v>
+        <v>91884</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2409,34 +2417,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>5449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508414</v>
+        <v>508953</v>
       </c>
       <c r="R17" t="n">
-        <v>7003632</v>
+        <v>7003530</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2482,15 +2490,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
-        </is>
-      </c>
-      <c r="AN17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal hård tallåga, hängande mot block</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2512,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119640299</v>
+        <v>119640294</v>
       </c>
       <c r="B18" t="n">
-        <v>78171</v>
+        <v>91856</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,21 +2528,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508959</v>
+        <v>508900</v>
       </c>
       <c r="R18" t="n">
-        <v>7003489</v>
+        <v>7003399</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2601,15 +2601,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>rikblockig 140-årig hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AN18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tallåga</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2742,10 +2734,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119640298</v>
+        <v>119640291</v>
       </c>
       <c r="B20" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2758,21 +2750,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2782,10 +2774,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508979</v>
+        <v>508847</v>
       </c>
       <c r="R20" t="n">
-        <v>7003452</v>
+        <v>7003454</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,15 +2823,15 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>rikblockig 140-årig hällmarkstallskog</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
         </is>
       </c>
       <c r="AN20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>2 substratenheter # bastanta gamla tallågor med kolade ytor</t>
+          <t>1 substratenheter # grov brandhögstubbe</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2861,10 +2853,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119640283</v>
+        <v>119640298</v>
       </c>
       <c r="B21" t="n">
-        <v>91834</v>
+        <v>78171</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2877,34 +2869,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508663</v>
+        <v>508979</v>
       </c>
       <c r="R21" t="n">
-        <v>7003642</v>
+        <v>7003452</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2950,7 +2942,15 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>rikblockig 140-årig hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>2 substratenheter # bastanta gamla tallågor med kolade ytor</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119640293</v>
+        <v>119640282</v>
       </c>
       <c r="B22" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2988,34 +2988,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>508895</v>
+        <v>508587</v>
       </c>
       <c r="R22" t="n">
-        <v>7003432</v>
+        <v>7003606</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>140-årig tallskog på häll med lav</t>
+          <t>140-årig stavatallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119640278</v>
+        <v>119640281</v>
       </c>
       <c r="B23" t="n">
-        <v>78171</v>
+        <v>90807</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3095,25 +3095,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3123,10 +3123,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>508542</v>
+        <v>508585</v>
       </c>
       <c r="R23" t="n">
-        <v>7003590</v>
+        <v>7003583</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
+          <t>140-årig stavatallskog på storblockig rismark</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal hård tallåga</t>
+          <t>1 substratenheter # grov gammal tallåga, troligen fallen torraka</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3202,10 +3202,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119640288</v>
+        <v>119640297</v>
       </c>
       <c r="B24" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3218,21 +3218,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>508941</v>
+        <v>508975</v>
       </c>
       <c r="R24" t="n">
-        <v>7003619</v>
+        <v>7003442</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3313,10 +3313,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119640284</v>
+        <v>119640299</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
+        <v>78171</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3329,21 +3329,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508846</v>
+        <v>508959</v>
       </c>
       <c r="R25" t="n">
-        <v>7003739</v>
+        <v>7003489</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>140-årig tallskog, i kant mot lok med lövträd</t>
+          <t>rikblockig 140-årig hällmarkstallskog</t>
         </is>
       </c>
       <c r="AN25" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal senvuxen sälg</t>
+          <t>1 substratenheter # gammal tallåga</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119640291</v>
+        <v>119640273</v>
       </c>
       <c r="B26" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3448,34 +3448,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508847</v>
+        <v>508454</v>
       </c>
       <c r="R26" t="n">
-        <v>7003454</v>
+        <v>7003691</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
+          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
         </is>
       </c>
       <c r="AN26" t="n">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov brandhögstubbe</t>
+          <t>1 substratenheter # gammal hård tallåga efter fallen torraka, hängande mot block</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 34816-2024 artfynd.xlsx
+++ b/artfynd/A 34816-2024 artfynd.xlsx
@@ -2401,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119640300</v>
+        <v>119640294</v>
       </c>
       <c r="B17" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508953</v>
+        <v>508900</v>
       </c>
       <c r="R17" t="n">
-        <v>7003530</v>
+        <v>7003399</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2512,7 +2512,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119640294</v>
+        <v>119640296</v>
       </c>
       <c r="B18" t="n">
         <v>91856</v>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508900</v>
+        <v>508950</v>
       </c>
       <c r="R18" t="n">
-        <v>7003399</v>
+        <v>7003342</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119640296</v>
+        <v>119640300</v>
       </c>
       <c r="B19" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,21 +2639,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508950</v>
+        <v>508953</v>
       </c>
       <c r="R19" t="n">
-        <v>7003342</v>
+        <v>7003530</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119640291</v>
+        <v>119640298</v>
       </c>
       <c r="B20" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2750,21 +2750,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508847</v>
+        <v>508979</v>
       </c>
       <c r="R20" t="n">
-        <v>7003454</v>
+        <v>7003452</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2823,15 +2823,15 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
+          <t>rikblockig 140-årig hällmarkstallskog</t>
         </is>
       </c>
       <c r="AN20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov brandhögstubbe</t>
+          <t>2 substratenheter # bastanta gamla tallågor med kolade ytor</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119640298</v>
+        <v>119640291</v>
       </c>
       <c r="B21" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2869,21 +2869,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508979</v>
+        <v>508847</v>
       </c>
       <c r="R21" t="n">
-        <v>7003452</v>
+        <v>7003454</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2942,15 +2942,15 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>rikblockig 140-årig hällmarkstallskog</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
         </is>
       </c>
       <c r="AN21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>2 substratenheter # bastanta gamla tallågor med kolade ytor</t>
+          <t>1 substratenheter # grov brandhögstubbe</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 34816-2024 artfynd.xlsx
+++ b/artfynd/A 34816-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119640271</v>
+        <v>119640302</v>
       </c>
       <c r="B5" t="n">
-        <v>90488</v>
+        <v>91856</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,34 +1024,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3242</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508504</v>
+        <v>508975</v>
       </c>
       <c r="R5" t="n">
-        <v>7003662</v>
+        <v>7003554</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,15 +1097,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>1 substratenheter # topp av fallen torraka, hängande mot block</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1127,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119640302</v>
+        <v>119640292</v>
       </c>
       <c r="B6" t="n">
-        <v>91856</v>
+        <v>78263</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508975</v>
+        <v>508847</v>
       </c>
       <c r="R6" t="n">
-        <v>7003554</v>
+        <v>7003454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,7 +1208,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>grov brandhögstubbe och andra brandstubbar</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1238,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119640292</v>
+        <v>119640289</v>
       </c>
       <c r="B7" t="n">
-        <v>78263</v>
+        <v>91832</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1278,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508847</v>
+        <v>508913</v>
       </c>
       <c r="R7" t="n">
-        <v>7003454</v>
+        <v>7003620</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,12 +1324,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>grov brandhögstubbe och andra brandstubbar</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1354,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119640289</v>
+        <v>119640295</v>
       </c>
       <c r="B8" t="n">
-        <v>91832</v>
+        <v>78263</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,21 +1362,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1394,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508913</v>
+        <v>508945</v>
       </c>
       <c r="R8" t="n">
-        <v>7003620</v>
+        <v>7003353</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1443,7 +1435,15 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119640278</v>
+        <v>119640283</v>
       </c>
       <c r="B9" t="n">
-        <v>78171</v>
+        <v>91834</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508542</v>
+        <v>508663</v>
       </c>
       <c r="R9" t="n">
-        <v>7003590</v>
+        <v>7003642</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,15 +1554,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
-        </is>
-      </c>
-      <c r="AN9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal hård tallåga</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1584,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119640275</v>
+        <v>119640286</v>
       </c>
       <c r="B10" t="n">
-        <v>78171</v>
+        <v>91856</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,34 +1592,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508414</v>
+        <v>508913</v>
       </c>
       <c r="R10" t="n">
-        <v>7003632</v>
+        <v>7003744</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,15 +1665,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
-        </is>
-      </c>
-      <c r="AN10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal hård tallåga, hängande mot block</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1703,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119640295</v>
+        <v>119640284</v>
       </c>
       <c r="B11" t="n">
-        <v>78263</v>
+        <v>79607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508945</v>
+        <v>508846</v>
       </c>
       <c r="R11" t="n">
-        <v>7003353</v>
+        <v>7003739</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,7 +1776,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
+          <t>140-årig tallskog, i kant mot lok med lövträd</t>
         </is>
       </c>
       <c r="AN11" t="n">
@@ -1800,7 +1784,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>1 substratenheter # gammal senvuxen sälg</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1822,10 +1806,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119640283</v>
+        <v>119640287</v>
       </c>
       <c r="B12" t="n">
-        <v>91834</v>
+        <v>78171</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,34 +1822,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508663</v>
+        <v>508935</v>
       </c>
       <c r="R12" t="n">
-        <v>7003642</v>
+        <v>7003749</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1912,6 +1896,14 @@
       <c r="AI12" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal torr tallåga</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1933,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119640286</v>
+        <v>119640285</v>
       </c>
       <c r="B13" t="n">
-        <v>91856</v>
+        <v>79473</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,21 +1941,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>388</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1973,10 +1965,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508913</v>
+        <v>508873</v>
       </c>
       <c r="R13" t="n">
-        <v>7003744</v>
+        <v>7003756</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,7 +2014,15 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grovbarkig, ca 200-årig asp</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2044,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119640284</v>
+        <v>119640294</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>91856</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,21 +2060,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508846</v>
+        <v>508900</v>
       </c>
       <c r="R14" t="n">
-        <v>7003739</v>
+        <v>7003399</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,15 +2133,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>140-årig tallskog, i kant mot lok med lövträd</t>
-        </is>
-      </c>
-      <c r="AN14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal senvuxen sälg</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2163,10 +2155,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119640287</v>
+        <v>119640296</v>
       </c>
       <c r="B15" t="n">
-        <v>78171</v>
+        <v>91856</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,21 +2171,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2203,10 +2195,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508935</v>
+        <v>508950</v>
       </c>
       <c r="R15" t="n">
-        <v>7003749</v>
+        <v>7003342</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2252,15 +2244,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal torr tallåga</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2282,10 +2266,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119640285</v>
+        <v>119640300</v>
       </c>
       <c r="B16" t="n">
-        <v>79473</v>
+        <v>91884</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2298,21 +2282,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>388</v>
+        <v>5449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2322,10 +2306,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508873</v>
+        <v>508953</v>
       </c>
       <c r="R16" t="n">
-        <v>7003756</v>
+        <v>7003530</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2371,15 +2355,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
-        </is>
-      </c>
-      <c r="AN16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grovbarkig, ca 200-årig asp</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2401,10 +2377,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119640294</v>
+        <v>119640298</v>
       </c>
       <c r="B17" t="n">
-        <v>91856</v>
+        <v>78171</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,21 +2393,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2441,10 +2417,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508900</v>
+        <v>508979</v>
       </c>
       <c r="R17" t="n">
-        <v>7003399</v>
+        <v>7003452</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2490,7 +2466,15 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>rikblockig 140-årig hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>2 substratenheter # bastanta gamla tallågor med kolade ytor</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2512,10 +2496,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119640296</v>
+        <v>119640291</v>
       </c>
       <c r="B18" t="n">
-        <v>91856</v>
+        <v>79144</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,21 +2512,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2552,10 +2536,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508950</v>
+        <v>508847</v>
       </c>
       <c r="R18" t="n">
-        <v>7003342</v>
+        <v>7003454</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2602,6 +2586,14 @@
       <c r="AI18" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med fattigris</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov brandhögstubbe</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2623,7 +2615,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119640300</v>
+        <v>119640297</v>
       </c>
       <c r="B19" t="n">
         <v>91884</v>
@@ -2663,10 +2655,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508953</v>
+        <v>508975</v>
       </c>
       <c r="R19" t="n">
-        <v>7003530</v>
+        <v>7003442</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2734,7 +2726,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119640298</v>
+        <v>119640299</v>
       </c>
       <c r="B20" t="n">
         <v>78171</v>
@@ -2774,10 +2766,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508979</v>
+        <v>508959</v>
       </c>
       <c r="R20" t="n">
-        <v>7003452</v>
+        <v>7003489</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2827,11 +2819,11 @@
         </is>
       </c>
       <c r="AN20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>2 substratenheter # bastanta gamla tallågor med kolade ytor</t>
+          <t>1 substratenheter # gammal tallåga</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2846,704 +2838,6 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>119640291</v>
-      </c>
-      <c r="B21" t="n">
-        <v>79144</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>508847</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7003454</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
-        </is>
-      </c>
-      <c r="AN21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov brandhögstubbe</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>119640282</v>
-      </c>
-      <c r="B22" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>2059</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Skrovlig taggsvamp</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Hydnellum scabrosum</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>508587</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7003606</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>140-årig stavatallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>119640281</v>
-      </c>
-      <c r="B23" t="n">
-        <v>90807</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>65</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Fläckporing</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Anthoporia albobrunnea</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>508585</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7003583</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>140-årig stavatallskog på storblockig rismark</t>
-        </is>
-      </c>
-      <c r="AN23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov gammal tallåga, troligen fallen torraka</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>119640297</v>
-      </c>
-      <c r="B24" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>508975</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7003442</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>119640299</v>
-      </c>
-      <c r="B25" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>353</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>508959</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7003489</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>rikblockig 140-årig hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AN25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tallåga</t>
-        </is>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>119640273</v>
-      </c>
-      <c r="B26" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>353</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>508454</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7003691</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>140-årig stavatallskog med spridda gammeltallar på storblockig mark</t>
-        </is>
-      </c>
-      <c r="AN26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal hård tallåga efter fallen torraka, hängande mot block</t>
-        </is>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 34816-2024 artfynd.xlsx
+++ b/artfynd/A 34816-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119640290</v>
+        <v>119640218</v>
       </c>
       <c r="B2" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Stenloken, väster om, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508875</v>
+        <v>508738</v>
       </c>
       <c r="R2" t="n">
-        <v>7003587</v>
+        <v>7003781</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +759,15 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig gallrad stavatallskog på småblockig mark med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov gammal tallåga av vindfälld gammal tall</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119640288</v>
+        <v>119640283</v>
       </c>
       <c r="B3" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,34 +800,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Orrviktjärnen, nordväst om, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508941</v>
+        <v>508663</v>
       </c>
       <c r="R3" t="n">
-        <v>7003619</v>
+        <v>7003642</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119640293</v>
+        <v>119640291</v>
       </c>
       <c r="B4" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508895</v>
+        <v>508847</v>
       </c>
       <c r="R4" t="n">
-        <v>7003432</v>
+        <v>7003454</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +979,15 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>140-årig tallskog på häll med lav</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov brandhögstubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,15 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119640302</v>
+        <v>62023319</v>
       </c>
       <c r="B5" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,34 +1020,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Stugusjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508975</v>
+        <v>508791</v>
       </c>
       <c r="R5" t="n">
-        <v>7003554</v>
+        <v>7003810</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,12 +1074,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2016-10-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2016-10-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,37 +1093,36 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1 substratenheter # sälg</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Johan Kjetselberg, Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119640292</v>
+        <v>119640284</v>
       </c>
       <c r="B6" t="n">
-        <v>78263</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508847</v>
+        <v>508846</v>
       </c>
       <c r="R6" t="n">
-        <v>7003454</v>
+        <v>7003739</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,12 +1203,15 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
-        </is>
+          <t>140-årig tallskog, i kant mot lok med lövträd</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>grov brandhögstubbe och andra brandstubbar</t>
+          <t>1 substratenheter # gammal senvuxen sälg</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1235,15 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119640289</v>
+        <v>119640217</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,34 +1244,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>101410</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, norr om, Jmt</t>
+          <t>Stenloken, väster om, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508913</v>
+        <v>508774</v>
       </c>
       <c r="R7" t="n">
-        <v>7003620</v>
+        <v>7003814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,12 +1298,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,7 +1317,15 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig gallrad stavatallskog på småblockig mark med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter # typiska spår i drygt 200-årig tall</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1346,15 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119640295</v>
+        <v>119640292</v>
       </c>
       <c r="B8" t="n">
-        <v>78263</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508945</v>
+        <v>508847</v>
       </c>
       <c r="R8" t="n">
-        <v>7003353</v>
+        <v>7003454</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,12 +1434,9 @@
           <t>140-årig tallskog på småblockig morän med fattigris</t>
         </is>
       </c>
-      <c r="AN8" t="n">
-        <v>1</v>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>grov brandhögstubbe och andra brandstubbar</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1465,15 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119640283</v>
+        <v>119640287</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,34 +1469,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, nordväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508663</v>
+        <v>508935</v>
       </c>
       <c r="R9" t="n">
-        <v>7003642</v>
+        <v>7003749</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,6 +1543,14 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal torr tallåga</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1576,15 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119640286</v>
+        <v>119640298</v>
       </c>
       <c r="B10" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1583,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508913</v>
+        <v>508979</v>
       </c>
       <c r="R10" t="n">
-        <v>7003744</v>
+        <v>7003452</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1656,15 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>rikblockig 140-årig hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>2 substratenheter # bastanta gamla tallågor med kolade ytor</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1687,15 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119640284</v>
+        <v>119640299</v>
       </c>
       <c r="B11" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,21 +1697,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,10 +1721,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508846</v>
+        <v>508959</v>
       </c>
       <c r="R11" t="n">
-        <v>7003739</v>
+        <v>7003489</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,7 +1770,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>140-årig tallskog, i kant mot lok med lövträd</t>
+          <t>rikblockig 140-årig hällmarkstallskog</t>
         </is>
       </c>
       <c r="AN11" t="n">
@@ -1784,7 +1778,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal senvuxen sälg</t>
+          <t>1 substratenheter # gammal tallåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1806,15 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119640287</v>
+        <v>119640285</v>
       </c>
       <c r="B12" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>388</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1846,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508935</v>
+        <v>508873</v>
       </c>
       <c r="R12" t="n">
-        <v>7003749</v>
+        <v>7003756</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1884,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
         </is>
       </c>
       <c r="AN12" t="n">
@@ -1903,7 +1892,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal torr tallåga</t>
+          <t>1 substratenheter # grovbarkig, ca 200-årig asp</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1925,37 +1914,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119640285</v>
+        <v>119640286</v>
       </c>
       <c r="B13" t="n">
-        <v>79473</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>388</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1965,10 +1949,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508873</v>
+        <v>508913</v>
       </c>
       <c r="R13" t="n">
-        <v>7003756</v>
+        <v>7003744</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,15 +1998,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
-        </is>
-      </c>
-      <c r="AN13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grovbarkig, ca 200-årig asp</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2044,19 +2020,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119640294</v>
+        <v>119640288</v>
       </c>
       <c r="B14" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2084,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508900</v>
+        <v>508941</v>
       </c>
       <c r="R14" t="n">
-        <v>7003399</v>
+        <v>7003619</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2155,19 +2126,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119640296</v>
+        <v>119640290</v>
       </c>
       <c r="B15" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2195,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508950</v>
+        <v>508875</v>
       </c>
       <c r="R15" t="n">
-        <v>7003342</v>
+        <v>7003587</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2244,7 +2210,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2266,37 +2232,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119640300</v>
+        <v>119640294</v>
       </c>
       <c r="B16" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2306,10 +2267,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508953</v>
+        <v>508900</v>
       </c>
       <c r="R16" t="n">
-        <v>7003530</v>
+        <v>7003399</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2377,37 +2338,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119640298</v>
+        <v>119640296</v>
       </c>
       <c r="B17" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2417,10 +2373,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508979</v>
+        <v>508950</v>
       </c>
       <c r="R17" t="n">
-        <v>7003452</v>
+        <v>7003342</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2466,15 +2422,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>rikblockig 140-årig hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AN17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>2 substratenheter # bastanta gamla tallågor med kolade ytor</t>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2496,37 +2444,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119640291</v>
+        <v>119640302</v>
       </c>
       <c r="B18" t="n">
-        <v>79144</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2536,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508847</v>
+        <v>508975</v>
       </c>
       <c r="R18" t="n">
-        <v>7003454</v>
+        <v>7003554</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2585,15 +2528,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med fattigris</t>
-        </is>
-      </c>
-      <c r="AN18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov brandhögstubbe</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2615,15 +2550,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119640297</v>
+        <v>119640289</v>
       </c>
       <c r="B19" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,21 +2561,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2655,10 +2585,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508975</v>
+        <v>508913</v>
       </c>
       <c r="R19" t="n">
-        <v>7003442</v>
+        <v>7003620</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2726,15 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119640299</v>
+        <v>119640293</v>
       </c>
       <c r="B20" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,21 +2667,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2766,10 +2691,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508959</v>
+        <v>508895</v>
       </c>
       <c r="R20" t="n">
-        <v>7003489</v>
+        <v>7003432</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,15 +2740,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>rikblockig 140-årig hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AN20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tallåga</t>
+          <t>140-årig tallskog på häll med lav</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2838,6 +2755,120 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>119640295</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Orrviktjärnen, norr om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>508945</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7003353</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>140-årig tallskog på småblockig morän med fattigris</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 34816-2024 artfynd.xlsx
+++ b/artfynd/A 34816-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640218</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640287</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640298</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640299</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640285</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640286</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1454,6 +1489,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640288</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640290</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1666,6 +1711,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640294</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1772,6 +1822,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640296</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1878,6 +1933,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640302</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1984,6 +2044,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640289</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2090,6 +2155,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640293</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2196,6 +2266,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640283</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2310,6 +2385,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640291</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2420,6 +2500,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62023319</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2534,6 +2619,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640284</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2648,6 +2738,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640217</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2759,6 +2854,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640292</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2873,8 +2973,35 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640295</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>